--- a/04_Figures/F04_association/modules/total/lm/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/total/lm/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.44885177668947</v>
+        <v>-10.3568513671072</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.181101370163182</v>
+        <v>-0.878429127234244</v>
       </c>
       <c r="F2" t="n">
-        <v>0.859310803086066</v>
+        <v>0.39695899671881</v>
       </c>
       <c r="G2" t="n">
-        <v>0.911267992894709</v>
+        <v>0.809832188795764</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-13.5861539282543</v>
+        <v>-0.508436291540751</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.33407035513133</v>
+        <v>-0.0388135034769199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.206946476909998</v>
+        <v>0.969677334211304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.728403015723148</v>
+        <v>0.969677334211304</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-19.2930916419893</v>
+        <v>-14.4426189577747</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.50735849890137</v>
+        <v>-1.50639601126046</v>
       </c>
       <c r="F4" t="n">
-        <v>0.15758515717784</v>
+        <v>0.157828986411187</v>
       </c>
       <c r="G4" t="n">
-        <v>0.728403015723148</v>
+        <v>0.578706283507684</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.47758063924598</v>
+        <v>13.3734917972015</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.115214609861581</v>
+        <v>1.07804242271113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.91018049887411</v>
+        <v>0.302208823684515</v>
       </c>
       <c r="G5" t="n">
-        <v>0.911267992894709</v>
+        <v>0.809832188795764</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>1.50902354850492</v>
+        <v>1.78388281660868</v>
       </c>
       <c r="E6" t="n">
-        <v>0.113813063646433</v>
+        <v>0.13335901798526</v>
       </c>
       <c r="F6" t="n">
-        <v>0.911267992894709</v>
+        <v>0.896119776873721</v>
       </c>
       <c r="G6" t="n">
-        <v>0.911267992894709</v>
+        <v>0.969677334211304</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-10.0280782409349</v>
+        <v>-2.77578592028331</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.00185990762479</v>
+        <v>-0.142755379320558</v>
       </c>
       <c r="F7" t="n">
-        <v>0.336186007256838</v>
+        <v>0.88885235208039</v>
       </c>
       <c r="G7" t="n">
-        <v>0.728403015723148</v>
+        <v>0.969677334211304</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>7.21124159397441</v>
+        <v>19.6415352569509</v>
       </c>
       <c r="E8" t="n">
-        <v>0.585403475082328</v>
+        <v>1.94013462383602</v>
       </c>
       <c r="F8" t="n">
-        <v>0.569121993452077</v>
+        <v>0.0762261768806251</v>
       </c>
       <c r="G8" t="n">
-        <v>0.822065101653</v>
+        <v>0.578706283507684</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>22.6809988534421</v>
+        <v>-3.32895890990767</v>
       </c>
       <c r="E9" t="n">
-        <v>2.15970679628502</v>
+        <v>-0.318072994584803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0517383989594104</v>
+        <v>0.755896743910648</v>
       </c>
       <c r="G9" t="n">
-        <v>0.672599186472336</v>
+        <v>0.969677334211304</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>14.2302023166772</v>
+        <v>-5.97775465707029</v>
       </c>
       <c r="E10" t="n">
-        <v>1.17090894459096</v>
+        <v>-0.670319090140353</v>
       </c>
       <c r="F10" t="n">
-        <v>0.26436226118149</v>
+        <v>0.515347756506395</v>
       </c>
       <c r="G10" t="n">
-        <v>0.728403015723148</v>
+        <v>0.809832188795764</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.25250154541505</v>
+        <v>7.3987360821477</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.36443124316543</v>
+        <v>0.683210146235661</v>
       </c>
       <c r="F11" t="n">
-        <v>0.721876980242566</v>
+        <v>0.507450952323453</v>
       </c>
       <c r="G11" t="n">
-        <v>0.911267992894709</v>
+        <v>0.809832188795764</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>11.6362274355227</v>
+        <v>-18.9917246866612</v>
       </c>
       <c r="E12" t="n">
-        <v>1.03060894002571</v>
+        <v>-1.50967093294301</v>
       </c>
       <c r="F12" t="n">
-        <v>0.323049612726274</v>
+        <v>0.157000658515896</v>
       </c>
       <c r="G12" t="n">
-        <v>0.728403015723148</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.27273150518333</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.671676461948735</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.514512875072737</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.822065101653</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-6.63738174400753</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.73620194537644</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.475753681649692</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.822065101653</v>
+        <v>0.578706283507684</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-1211.32517087819</v>
+        <v>-591.336974242055</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.374967906785607</v>
+        <v>-0.286291754206596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.714227477028356</v>
+        <v>0.779537228436124</v>
       </c>
       <c r="G2" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-561.677900321565</v>
+        <v>-1936.85343542193</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.303211927978387</v>
+        <v>-0.896262613207821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.766920738618405</v>
+        <v>0.387738894502999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-638.395149856023</v>
+        <v>-711.914004079463</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.26922012316449</v>
+        <v>-0.402318361553852</v>
       </c>
       <c r="F4" t="n">
-        <v>0.792333457909833</v>
+        <v>0.694523890852993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-2075.90300138499</v>
+        <v>1812.41521822623</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.987257323197667</v>
+        <v>0.842569491360835</v>
       </c>
       <c r="F5" t="n">
-        <v>0.343005262543262</v>
+        <v>0.415947055928424</v>
       </c>
       <c r="G5" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>708.122898313801</v>
+        <v>827.809282961461</v>
       </c>
       <c r="E6" t="n">
-        <v>0.31455964486406</v>
+        <v>0.364930986236604</v>
       </c>
       <c r="F6" t="n">
-        <v>0.758498004985191</v>
+        <v>0.721513453783256</v>
       </c>
       <c r="G6" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-1358.99222240584</v>
+        <v>-1224.07214025075</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.784841941991862</v>
+        <v>-0.371256755308409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.447764069962123</v>
+        <v>0.71691808728164</v>
       </c>
       <c r="G7" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>621.48359676119</v>
+        <v>1576.39326264678</v>
       </c>
       <c r="E8" t="n">
-        <v>0.292993348523541</v>
+        <v>0.819304562886028</v>
       </c>
       <c r="F8" t="n">
-        <v>0.774532120130289</v>
+        <v>0.42858506218412</v>
       </c>
       <c r="G8" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1979.36737654279</v>
+        <v>-312.825181416275</v>
       </c>
       <c r="E9" t="n">
-        <v>0.975133673726946</v>
+        <v>-0.174903795084634</v>
       </c>
       <c r="F9" t="n">
-        <v>0.348742253313373</v>
+        <v>0.864071602612297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.814027657340465</v>
+        <v>0.864071602612297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>1925.87894789603</v>
+        <v>-437.265192818599</v>
       </c>
       <c r="E10" t="n">
-        <v>0.911003633036605</v>
+        <v>-0.283468406947796</v>
       </c>
       <c r="F10" t="n">
-        <v>0.38022966992674</v>
+        <v>0.781648964076325</v>
       </c>
       <c r="G10" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-1554.36706183409</v>
+        <v>525.082970327464</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.640107572576069</v>
+        <v>0.280093244196315</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5341340273444</v>
+        <v>0.7841758189838</v>
       </c>
       <c r="G11" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>481.50019076189</v>
+        <v>-689.322792948124</v>
       </c>
       <c r="E12" t="n">
-        <v>0.240466506403759</v>
+        <v>-0.295875072871118</v>
       </c>
       <c r="F12" t="n">
-        <v>0.814027657340465</v>
+        <v>0.772383128651381</v>
       </c>
       <c r="G12" t="n">
-        <v>0.814027657340465</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>527.399166898257</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.281557491970063</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.783079275278755</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.814027657340465</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-721.844859689035</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.46372181399046</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.6511457445107</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.814027657340465</v>
+        <v>0.86259340088218</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-1124.94073900446</v>
+        <v>-884.539939422603</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.374218630574033</v>
+        <v>-0.462728225649601</v>
       </c>
       <c r="F2" t="n">
-        <v>0.714770385703841</v>
+        <v>0.651837698656748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-697.134401200478</v>
+        <v>-2156.47773608184</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.405646719569078</v>
+        <v>-1.08823589448405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.692141575998766</v>
+        <v>0.297864599918844</v>
       </c>
       <c r="G3" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>88.184400598843</v>
+        <v>-715.738386929799</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0398477007786907</v>
+        <v>-0.435170819841089</v>
       </c>
       <c r="F4" t="n">
-        <v>0.968869834914349</v>
+        <v>0.671162241367244</v>
       </c>
       <c r="G4" t="n">
-        <v>0.968869834914349</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-2276.74163942359</v>
+        <v>2478.8501363482</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.18245447506566</v>
+        <v>1.28325777980686</v>
       </c>
       <c r="F5" t="n">
-        <v>0.259925509715309</v>
+        <v>0.223630913299728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>951.371578509063</v>
+        <v>1064.80848689264</v>
       </c>
       <c r="E6" t="n">
-        <v>0.456213112739023</v>
+        <v>0.507026442106109</v>
       </c>
       <c r="F6" t="n">
-        <v>0.656383316196461</v>
+        <v>0.621324352201494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-1354.79984829662</v>
+        <v>-1175.82933967378</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.844046547555047</v>
+        <v>-0.383396302611208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.415153144262865</v>
+        <v>0.708131764700431</v>
       </c>
       <c r="G7" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>96.0572940356129</v>
+        <v>1463.72307651578</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0484981924379438</v>
+        <v>0.817447902677206</v>
       </c>
       <c r="F8" t="n">
-        <v>0.962117048791712</v>
+        <v>0.429604411817303</v>
       </c>
       <c r="G8" t="n">
-        <v>0.968869834914349</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1821.01183563192</v>
+        <v>-861.820986007188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.963243710370892</v>
+        <v>-0.523032749347142</v>
       </c>
       <c r="F9" t="n">
-        <v>0.354435179810475</v>
+        <v>0.610473329265713</v>
       </c>
       <c r="G9" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>2520.63124322654</v>
+        <v>-802.539772717812</v>
       </c>
       <c r="E10" t="n">
-        <v>1.32704812199955</v>
+        <v>-0.56460237913667</v>
       </c>
       <c r="F10" t="n">
-        <v>0.209189876530258</v>
+        <v>0.582744535951839</v>
       </c>
       <c r="G10" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-1472.4523777699</v>
+        <v>580.351484141463</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.652053167887224</v>
+        <v>0.333136519237391</v>
       </c>
       <c r="F11" t="n">
-        <v>0.526659506991026</v>
+        <v>0.744779558167505</v>
       </c>
       <c r="G11" t="n">
-        <v>0.93491883289536</v>
+        <v>0.819257513984256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>504.393133462538</v>
+        <v>2.59858816448811</v>
       </c>
       <c r="E12" t="n">
-        <v>0.270881687670368</v>
+        <v>0.00119431060600551</v>
       </c>
       <c r="F12" t="n">
-        <v>0.791085166296073</v>
+        <v>0.999066703099615</v>
       </c>
       <c r="G12" t="n">
-        <v>0.93491883289536</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>587.05956575343</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.337288379457459</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.741725801328227</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.93491883289536</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-1172.03127872046</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.824386548730411</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.425803066087561</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.93491883289536</v>
+        <v>0.999066703099615</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.92158555780889</v>
+        <v>-1.52728730003724</v>
       </c>
       <c r="E2" t="n">
-        <v>0.488178614876962</v>
+        <v>-0.611686001199183</v>
       </c>
       <c r="F2" t="n">
-        <v>0.634221804028889</v>
+        <v>0.552158365220505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.93147203942939</v>
+        <v>0.860951986143003</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.1507994165226</v>
+        <v>4.46225756883525</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.51109829693879</v>
+        <v>1.85319557248402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.156640799175879</v>
+        <v>0.0885927015957618</v>
       </c>
       <c r="G3" t="n">
-        <v>0.509082597321605</v>
+        <v>0.279896945104582</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-6.76077381615861</v>
+        <v>-3.43788422561775</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.13280417402385</v>
+        <v>-1.77188387865164</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00864670543104142</v>
+        <v>0.101780707310757</v>
       </c>
       <c r="G4" t="n">
-        <v>0.112407170603538</v>
+        <v>0.279896945104582</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>4.59057099751467</v>
+        <v>-0.308648253835753</v>
       </c>
       <c r="E5" t="n">
-        <v>1.97576322231414</v>
+        <v>-0.11402788162282</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0716324234009206</v>
+        <v>0.911101298128535</v>
       </c>
       <c r="G5" t="n">
-        <v>0.310407168070656</v>
+        <v>0.95985929065851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0226935601542</v>
+        <v>-1.07746348378773</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.371955356013899</v>
+        <v>-0.388549322875099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.716411292406656</v>
+        <v>0.70441526138973</v>
       </c>
       <c r="G6" t="n">
-        <v>0.93147203942939</v>
+        <v>0.860951986143003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.00744903893954</v>
+        <v>2.34371142590711</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.468049566758101</v>
+        <v>0.585952169792278</v>
       </c>
       <c r="F7" t="n">
-        <v>0.648135777322182</v>
+        <v>0.56876498989511</v>
       </c>
       <c r="G7" t="n">
-        <v>0.93147203942939</v>
+        <v>0.860951986143003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>3.08190528989087</v>
+        <v>4.06490095002417</v>
       </c>
       <c r="E8" t="n">
-        <v>1.25919410849519</v>
+        <v>1.92188633225007</v>
       </c>
       <c r="F8" t="n">
-        <v>0.231903193135422</v>
+        <v>0.0786825485956562</v>
       </c>
       <c r="G8" t="n">
-        <v>0.602948302152096</v>
+        <v>0.279896945104582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>4.60451322509203</v>
+        <v>0.969660808118962</v>
       </c>
       <c r="E9" t="n">
-        <v>2.08259917643517</v>
+        <v>0.446255360705942</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0593489442685445</v>
+        <v>0.663358666111719</v>
       </c>
       <c r="G9" t="n">
-        <v>0.310407168070656</v>
+        <v>0.860951986143003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0503250267250733</v>
+        <v>-0.0972940374134403</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0188193644532704</v>
+        <v>-0.0513912806749277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.985294498892691</v>
+        <v>0.95985929065851</v>
       </c>
       <c r="G10" t="n">
-        <v>0.985294498892691</v>
+        <v>0.95985929065851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.11088365129727</v>
+        <v>0.897229806693934</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0367067122968638</v>
+        <v>0.392443797951834</v>
       </c>
       <c r="F11" t="n">
-        <v>0.971322420397462</v>
+        <v>0.701611728008175</v>
       </c>
       <c r="G11" t="n">
-        <v>0.985294498892691</v>
+        <v>0.860951986143003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>2.48274548731738</v>
+        <v>-6.53064762763233</v>
       </c>
       <c r="E12" t="n">
-        <v>1.05712542048706</v>
+        <v>-3.03551960883836</v>
       </c>
       <c r="F12" t="n">
-        <v>0.311271772175472</v>
+        <v>0.0103597755312041</v>
       </c>
       <c r="G12" t="n">
-        <v>0.674422173046856</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.849944742547599</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.371809689636223</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.716516953407223</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.93147203942939</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.404160351702205</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.210745189879045</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.836622351603401</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.985294498892691</v>
+        <v>0.113957530843245</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-64.4760482453698</v>
+        <v>-22.8383509793066</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.942507973396174</v>
+        <v>-0.510506334711653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.364521284615111</v>
+        <v>0.618957207899527</v>
       </c>
       <c r="G2" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0813630165350969</v>
+        <v>10.8632350434227</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00200541341730453</v>
+        <v>0.223514097491026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.998432865587978</v>
+        <v>0.826895225791158</v>
       </c>
       <c r="G3" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>20.327775943847</v>
+        <v>10.4293680260078</v>
       </c>
       <c r="E4" t="n">
-        <v>0.394248402731085</v>
+        <v>0.26913669787259</v>
       </c>
       <c r="F4" t="n">
-        <v>0.700314189374166</v>
+        <v>0.792396149118026</v>
       </c>
       <c r="G4" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>17.0437629465229</v>
+        <v>45.4984557805024</v>
       </c>
       <c r="E5" t="n">
-        <v>0.359193567486166</v>
+        <v>0.978859034615611</v>
       </c>
       <c r="F5" t="n">
-        <v>0.725691258245751</v>
+        <v>0.346972103204596</v>
       </c>
       <c r="G5" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-39.613665657381</v>
+        <v>-37.3452703373266</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.825717298937393</v>
+        <v>-0.768654525047833</v>
       </c>
       <c r="F6" t="n">
-        <v>0.425076552197555</v>
+        <v>0.456960106074694</v>
       </c>
       <c r="G6" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.94088027281037</v>
+        <v>-66.27458425007</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.101777364067784</v>
+        <v>-0.9498408293483</v>
       </c>
       <c r="F7" t="n">
-        <v>0.920614278221134</v>
+        <v>0.360931558325769</v>
       </c>
       <c r="G7" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.55650109113188</v>
+        <v>-27.6357074191107</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.184487359237331</v>
+        <v>-0.651874239991226</v>
       </c>
       <c r="F8" t="n">
-        <v>0.856712208349096</v>
+        <v>0.526771018409895</v>
       </c>
       <c r="G8" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.5417855673265</v>
+        <v>4.21675421629965</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.607755671522535</v>
+        <v>0.107971462595706</v>
       </c>
       <c r="F9" t="n">
-        <v>0.554677230945703</v>
+        <v>0.915802630234251</v>
       </c>
       <c r="G9" t="n">
-        <v>0.998432865587978</v>
+        <v>0.915802630234251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>49.3416696170978</v>
+        <v>33.7118273469216</v>
       </c>
       <c r="E10" t="n">
-        <v>1.08404108927712</v>
+        <v>1.04254755471298</v>
       </c>
       <c r="F10" t="n">
-        <v>0.299646598773283</v>
+        <v>0.317706757669663</v>
       </c>
       <c r="G10" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.3492346419436</v>
+        <v>-20.4913666986443</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.342224322758666</v>
+        <v>-0.504621193738584</v>
       </c>
       <c r="F11" t="n">
-        <v>0.738101309959728</v>
+        <v>0.622963078698599</v>
       </c>
       <c r="G11" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.15089590452743</v>
+        <v>20.5420755442336</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0262807650038961</v>
+        <v>0.405397100711005</v>
       </c>
       <c r="F12" t="n">
-        <v>0.979465388357302</v>
+        <v>0.692320125027314</v>
       </c>
       <c r="G12" t="n">
-        <v>0.998432865587978</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-21.2692821133327</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.524626351963629</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.60939820273861</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.998432865587978</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>27.8662400897352</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.836604251548635</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.419163633668294</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.998432865587978</v>
+        <v>0.909584748370274</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.72658324716614</v>
+        <v>-4.25735750183774</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.134652330822157</v>
+        <v>-0.505949403212075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8953189736993</v>
+        <v>0.622877607364691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9948617138318</v>
+        <v>0.917691329543268</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-7.37091415533523</v>
+        <v>-0.715729876360636</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.989705433654895</v>
+        <v>-0.0794051141630002</v>
       </c>
       <c r="F3" t="n">
-        <v>0.343589100632566</v>
+        <v>0.938136553504468</v>
       </c>
       <c r="G3" t="n">
-        <v>0.722442012176849</v>
+        <v>0.970141540857853</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-8.89779356293004</v>
+        <v>-8.89360189560615</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.988524224474996</v>
+        <v>-1.2976511094627</v>
       </c>
       <c r="F4" t="n">
-        <v>0.344141667111647</v>
+        <v>0.22095958458905</v>
       </c>
       <c r="G4" t="n">
-        <v>0.722442012176849</v>
+        <v>0.765979380057234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0590078153751548</v>
+        <v>0.356591971184973</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00658777137062245</v>
+        <v>0.0382912862974269</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9948617138318</v>
+        <v>0.970141540857853</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9948617138318</v>
+        <v>0.970141540857853</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>7.7590571654092</v>
+        <v>6.97533696407591</v>
       </c>
       <c r="E6" t="n">
-        <v>0.896846606944398</v>
+        <v>0.792997691793259</v>
       </c>
       <c r="F6" t="n">
-        <v>0.389007237325996</v>
+        <v>0.444547030067966</v>
       </c>
       <c r="G6" t="n">
-        <v>0.722442012176849</v>
+        <v>0.854362474394118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.32355935926166</v>
+        <v>-1.95854023354555</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.926998817908215</v>
+        <v>-0.149596881711692</v>
       </c>
       <c r="F7" t="n">
-        <v>0.373819374618748</v>
+        <v>0.883790251607087</v>
       </c>
       <c r="G7" t="n">
-        <v>0.722442012176849</v>
+        <v>0.970141540857853</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>1.35776919386549</v>
+        <v>11.2918952541572</v>
       </c>
       <c r="E8" t="n">
-        <v>0.154081538578091</v>
+        <v>1.57151956032972</v>
       </c>
       <c r="F8" t="n">
-        <v>0.880335981759675</v>
+        <v>0.144362835266293</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9948617138318</v>
+        <v>0.765979380057234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>12.5073551765636</v>
+        <v>-3.34277383527738</v>
       </c>
       <c r="E9" t="n">
-        <v>1.67154155749611</v>
+        <v>-0.441488855752028</v>
       </c>
       <c r="F9" t="n">
-        <v>0.122787740293595</v>
+        <v>0.667411876031468</v>
       </c>
       <c r="G9" t="n">
-        <v>0.722442012176849</v>
+        <v>0.917691329543268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.197241918334162</v>
+        <v>-9.93678004171167</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0215970255550446</v>
+        <v>-1.67883577900421</v>
       </c>
       <c r="F10" t="n">
-        <v>0.98315619094674</v>
+        <v>0.121332401638097</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9948617138318</v>
+        <v>0.765979380057234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>5.09385140502563</v>
+        <v>8.26494766118631</v>
       </c>
       <c r="E11" t="n">
-        <v>0.515296525111915</v>
+        <v>1.13990731592933</v>
       </c>
       <c r="F11" t="n">
-        <v>0.616543061900057</v>
+        <v>0.278537956384449</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9948617138318</v>
+        <v>0.765979380057234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.907294432414979</v>
+        <v>-6.79739740142915</v>
       </c>
       <c r="E12" t="n">
-        <v>0.105447127421101</v>
+        <v>-0.755158253543538</v>
       </c>
       <c r="F12" t="n">
-        <v>0.917919322673075</v>
+        <v>0.466015895124064</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9948617138318</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.22784712778905</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.13782820413066</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.279368797457592</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.722442012176849</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-8.86784350107485</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.42513915215247</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.181868237772408</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.722442012176849</v>
+        <v>0.854362474394118</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2501,24 +2219,24 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.27273150518333</v>
+        <v>7.3987360821477</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.32355935926166</v>
+        <v>6.79739740142915</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>20.327775943847</v>
+        <v>22.8383509793066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>721.844859689035</v>
+        <v>711.914004079463</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,24 +2323,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1124.94073900446</v>
+        <v>884.539939422603</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2631,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92158555780889</v>
+        <v>1.52728730003724</v>
       </c>
     </row>
   </sheetData>
